--- a/public/certificate/prompathon.xlsx
+++ b/public/certificate/prompathon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,6 +454,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
@@ -477,14 +485,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1050,28 +1050,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1195,7 +1195,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1209,19 +1209,20 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1284,7 +1285,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1298,7 +1299,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1312,7 +1313,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1326,7 +1327,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1340,7 +1341,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1354,7 +1355,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1368,7 +1369,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1382,7 +1383,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1396,7 +1397,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1410,7 +1411,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1424,7 +1425,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1438,7 +1439,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1452,7 +1453,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1466,7 +1467,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1480,7 +1481,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1494,7 +1495,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1508,7 +1509,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1537,7 +1538,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{56F97E56-BE84-4FC0-992C-F825E5827808}">
+    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{DAD07797-2014-4A9D-920C-E9F6BAC5CC25}">
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
       <tableStyleElement type="secondRowStripe" dxfId="17"/>
     </tableStyle>
@@ -1824,16 +1825,16 @@
       <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="11" t="s">
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="14"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="5">
@@ -1872,15 +1873,15 @@
       <c r="L3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="13" t="s">
+      <c r="M3" s="13"/>
+      <c r="N3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="10">
         <v>609512592056</v>
       </c>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="15"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="1">
@@ -1916,16 +1917,16 @@
       <c r="K4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="12" t="s">
         <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="16">
+      <c r="P4" s="11"/>
+      <c r="Q4" s="17">
         <v>9899728185</v>
       </c>
     </row>
@@ -1963,16 +1964,16 @@
       <c r="K5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="13" t="s">
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="10">
         <v>609726255713</v>
       </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="17">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="18">
         <v>9984938255</v>
       </c>
     </row>
@@ -2010,16 +2011,16 @@
       <c r="K6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="11" t="s">
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <v>125934710744</v>
       </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="16">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="17">
         <v>9219055139</v>
       </c>
     </row>
@@ -2057,16 +2058,16 @@
       <c r="K7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13" t="s">
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="10">
         <v>609707257158</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="17">
+      <c r="P7" s="13"/>
+      <c r="Q7" s="18">
         <v>9266893243</v>
       </c>
     </row>
@@ -2074,7 +2075,7 @@
       <c r="A8" s="1">
         <v>46119.9018499421</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2107,15 +2108,15 @@
       <c r="L8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11" t="s">
+      <c r="M8" s="11"/>
+      <c r="N8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="9">
         <v>646316292410</v>
       </c>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="16">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="17">
         <v>7017673407</v>
       </c>
     </row>
@@ -2153,16 +2154,16 @@
       <c r="K9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="13" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <v>624709248500</v>
       </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="17">
+      <c r="P9" s="13"/>
+      <c r="Q9" s="18">
         <v>8920447645</v>
       </c>
     </row>
@@ -2200,16 +2201,16 @@
       <c r="K10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="11" t="s">
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <v>104926648390</v>
       </c>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="16">
+      <c r="P10" s="11"/>
+      <c r="Q10" s="17">
         <v>7500261134</v>
       </c>
     </row>
@@ -2235,7 +2236,7 @@
       <c r="G11" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -2247,16 +2248,16 @@
       <c r="K11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="13" t="s">
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="10">
         <v>646415982255</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="17">
+      <c r="P11" s="13"/>
+      <c r="Q11" s="18">
         <v>8090249844</v>
       </c>
     </row>
@@ -2294,16 +2295,16 @@
       <c r="K12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="11" t="s">
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <v>646453034619</v>
       </c>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="16">
+      <c r="P12" s="11"/>
+      <c r="Q12" s="17">
         <v>9984249543</v>
       </c>
     </row>
@@ -2344,15 +2345,15 @@
       <c r="L13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="13" t="s">
+      <c r="M13" s="13"/>
+      <c r="N13" s="14" t="s">
         <v>84</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="17">
+      <c r="P13" s="13"/>
+      <c r="Q13" s="18">
         <v>8595624282</v>
       </c>
     </row>
@@ -2393,15 +2394,15 @@
       <c r="L14" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="11" t="s">
+      <c r="M14" s="11"/>
+      <c r="N14" s="12" t="s">
         <v>91</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="16">
+      <c r="P14" s="11"/>
+      <c r="Q14" s="17">
         <v>7518668226</v>
       </c>
     </row>
@@ -2430,23 +2431,23 @@
       <c r="H15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="12"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="6" t="s">
         <v>94</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="13" t="s">
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <v>609844333744</v>
       </c>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="17">
+      <c r="P15" s="13"/>
+      <c r="Q15" s="18">
         <v>7905079690</v>
       </c>
     </row>
@@ -2487,15 +2488,15 @@
       <c r="L16" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="11" t="s">
+      <c r="M16" s="11"/>
+      <c r="N16" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="9">
         <v>609845429986</v>
       </c>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="16">
+      <c r="P16" s="11"/>
+      <c r="Q16" s="17">
         <v>9266877756</v>
       </c>
     </row>
@@ -2536,15 +2537,15 @@
       <c r="L17" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="13" t="s">
+      <c r="M17" s="13"/>
+      <c r="N17" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>609846235006</v>
       </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="17">
+      <c r="P17" s="13"/>
+      <c r="Q17" s="18">
         <v>9693989125</v>
       </c>
     </row>
@@ -2564,7 +2565,7 @@
       <c r="E18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>6386011818</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -2582,16 +2583,16 @@
       <c r="K18" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="11" t="s">
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="9">
         <v>609832716591</v>
       </c>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="16">
+      <c r="P18" s="11"/>
+      <c r="Q18" s="17">
         <v>6386011818</v>
       </c>
     </row>
@@ -2611,7 +2612,7 @@
       <c r="E19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="10">
         <v>8285530974</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -2629,16 +2630,16 @@
       <c r="K19" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="13" t="s">
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="10">
         <v>609858087546</v>
       </c>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="17">
+      <c r="P19" s="13"/>
+      <c r="Q19" s="18">
         <v>8285530974</v>
       </c>
     </row>
@@ -2676,16 +2677,16 @@
       <c r="K20" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="11" t="s">
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="9">
         <v>641636413979</v>
       </c>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="16">
+      <c r="P20" s="11"/>
+      <c r="Q20" s="17">
         <v>7827469526</v>
       </c>
     </row>
@@ -2723,16 +2724,16 @@
       <c r="K21" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="13" t="s">
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="10">
         <v>453685078959</v>
       </c>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="17">
+      <c r="P21" s="13"/>
+      <c r="Q21" s="18">
         <v>8586001883</v>
       </c>
     </row>
@@ -2758,6 +2759,7 @@
     <hyperlink ref="N19" r:id="rId19" display="https://drive.google.com/open?id=1T57VTCNMv18FkYyRpVtq_LIUBm6Sfhlj"/>
     <hyperlink ref="N20" r:id="rId20" display="https://drive.google.com/open?id=1MCeu5rJmAVPOcaya75_5kI3Iw2x2Pv4d"/>
     <hyperlink ref="N21" r:id="rId21" display="https://drive.google.com/open?id=1DDEzhkJdGEcgD5xbskkxetcOJWd5AAUe"/>
+    <hyperlink ref="B8" r:id="rId22" display="anshmittal647@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
